--- a/mock/TEST_p1.xlsx
+++ b/mock/TEST_p1.xlsx
@@ -43,7 +43,7 @@
     <t>PS1:BR207</t>
   </si>
   <si>
-    <t>PS1:BX218</t>
+    <t>SS11:JJ113.H</t>
   </si>
   <si>
     <t>PS2:CF318</t>
@@ -55,7 +55,7 @@
     <t>PS1:BP218</t>
   </si>
   <si>
-    <t>PS1:CJ219</t>
+    <t>SS4:FF113.A</t>
   </si>
   <si>
     <t>PS2:BR320</t>
@@ -67,10 +67,10 @@
     <t>PS1:BV305</t>
   </si>
   <si>
-    <t>PS2:BN313</t>
+    <t>SS4:NQ233.B</t>
   </si>
   <si>
-    <t>PS2:BW311</t>
+    <t>SS4:NQ233.D</t>
   </si>
   <si>
     <t>PS2:CH214</t>
@@ -112,7 +112,7 @@
     <t>PS1:BF216</t>
   </si>
   <si>
-    <t>PS1:BD123</t>
+    <t>SS4:LQ333.A</t>
   </si>
   <si>
     <t>PS1:CE216</t>
